--- a/inmobiliarias-santiago/inmobiliarias_ds19_ds49.xlsx
+++ b/inmobiliarias-santiago/inmobiliarias_ds19_ds49.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DS19'!$A$4:$K$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DS49'!$A$4:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DS49'!$A$4:$K$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2248,7 +2248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2965,12 +2965,12 @@
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Fundación Deportistas por un Sueño</t>
+          <t>Entidad Patrocinante Jessica Sandoval Quiroga E.I.R.L.</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Fundación</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
@@ -3015,24 +3015,24 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Grupo Vías</t>
+          <t>Entidad Patrocinante Kutralwe Ltda</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
+          <t>DS49</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
@@ -3072,19 +3072,19 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Huechuraba</t>
+          <t>Entidad Patrocinante Manuel Medina E.I.R.L.</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Municipio / Entidad Patrocinante</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -3092,9 +3092,9 @@
           <t>DS49</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>huechuraba.cl</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -3129,19 +3129,19 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Inmobiliaria y Constructora INSOC Ltda</t>
+          <t>Evolutiva Entidad Patrocinante y Consultora de Vivienda y Urbanismo SpA</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Constructora / Entidad Patrocinante</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -3186,34 +3186,34 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>TECHO-Chile (Inmobiliaria Social)</t>
+          <t>Fundación Deportistas por un Sueño</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Fundación / desarrolladora</t>
+          <t>Fundación</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>DS49 colectivo</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>cl.techo.org</t>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -3243,34 +3243,34 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Página Inmobiliaria Social</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
+          <t>Gestora Mashogar Ltda</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Fundación / Entidad Patrocinante</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DS49 / DS19</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>urbanismosocial.cl</t>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
@@ -3300,69 +3300,525 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>Grupo Vías</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Inmobiliaria</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
+        <is>
+          <t>Por confirmar</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Nómina de socios ADVS</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ilustre Municipalidad de Huechuraba</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Municipio / Entidad Patrocinante</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>huechuraba.cl</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Huechuraba</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Nómina MINVU de entidades patrocinantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Inmobiliaria D&amp;M SpA</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Patrocinante / Inmobiliaria</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Inmobiliaria y Constructora INSOC Ltda</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Constructora / Entidad Patrocinante</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Región Metropolitana</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Nómina MINVU de entidades patrocinantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Nahuen Ingenieros Constructores Asociados SpA</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Patrocinante / Constructora</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TECHO-Chile (Inmobiliaria Social)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Fundación / desarrolladora</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>DS49 colectivo</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>cl.techo.org</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>No publicado (formulario web)</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Página Inmobiliaria Social</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Fundación / Entidad Patrocinante</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>DS49 / DS19</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>urbanismosocial.cl</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>No publicado (formulario web)</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Santiago</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="inlineStr">
+        <is>
+          <t>Sitio corporativo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>Urbanitas</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Inmobiliaria</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>DS19 / DS49</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>Por confirmar</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>ADVS</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J29" s="13" t="inlineStr">
         <is>
           <t>sin dato</t>
         </is>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Ávalos y Ibacache Arquitectos Sociales Ltda</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Entidad Patrocinante</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>No publicado</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="I30" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>sin dato</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="inlineStr">
+        <is>
+          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:K22"/>
+  <autoFilter ref="A4:K30"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -3373,9 +3829,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3427,7 +3883,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -3437,7 +3893,7 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">

--- a/inmobiliarias-santiago/inmobiliarias_ds19_ds49.xlsx
+++ b/inmobiliarias-santiago/inmobiliarias_ds19_ds49.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DS19'!$A$4:$K$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DS49'!$A$4:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'DS49'!$A$4:$K$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -777,7 +777,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Inmobiliaria ICuadra</t>
+          <t>Consolida</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -787,27 +787,27 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DS19 / privados</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>icuadra.cl</t>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>contacto@icuadra.cl</t>
+          <t>contacto@consolida.cl</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>600 006 1030</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Alonso de Córdova 5670 of. 803 Las Condes</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -827,44 +827,44 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Página de contacto</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Inmobiliaria Koyam</t>
+          <t>Constructora OVAL (entidad patrocinante)</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Constructora / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>DS19 / DS1</t>
+          <t>DS49 / DS19</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>koyam.cl</t>
+          <t>constructoraoval.cl</t>
         </is>
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>contacto@koyam.cl</t>
+          <t>ggajardo@constructoraoval.cl</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2896 9410</t>
+          <t>+56 2 2343 0660</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>Av. Francisco Bilbao 1902 Providencia</t>
+          <t>Av. Pdte. Kennedy 5682 Vitacura</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr">
@@ -884,14 +884,14 @@
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Ficha directorio + sitio</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>iSiete Grupo Inmobiliario</t>
+          <t>Identidades</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
@@ -901,27 +901,27 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS1</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>isiete.cl</t>
+          <t>DS19</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>contacto@isiete.cl</t>
+          <t>fmella@consultoraidentidades.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>+56 9 3313 1363</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Santiago (dirección no publicada)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -941,14 +941,14 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Página de contacto corporativa</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>IVL Inversiones Inmobiliarias</t>
+          <t>Inmobiliaria ICuadra</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -958,37 +958,37 @@
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>DS19</t>
+          <t>DS19 / privados</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>ivl.cl</t>
+          <t>icuadra.cl</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>contacto@ivl.cl</t>
+          <t>contacto@icuadra.cl</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>600 006 1030</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Alonso de Córdova 5670 of. 803 Las Condes</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>No — Valparaíso/Concepción/Frutillar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pilares (Grupo Socovesa)</t>
+          <t>Inmobiliaria Koyam</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>pilares.cl</t>
+          <t>koyam.cl</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>servicioalcliente@pilares.cl</t>
+          <t>contacto@koyam.cl</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>+56 2 2840 7832</t>
+          <t>+56 2 2896 9410</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Providencia</t>
+          <t>Av. Francisco Bilbao 1902 Providencia</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
@@ -1055,14 +1055,14 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Página de postventa</t>
+          <t>Ficha directorio + sitio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Siena Inmobiliaria</t>
+          <t>iSiete Grupo Inmobiliario</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -1077,22 +1077,22 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>siena.cl</t>
+          <t>isiete.cl</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>informes@sienainmobiliaria.com</t>
+          <t>contacto@isiete.cl</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 9 3313 1363</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Los Militares 6191 piso 12 Las Condes</t>
+          <t>Santiago (dirección no publicada)</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
@@ -1112,14 +1112,14 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Página de contacto</t>
+          <t>Página de contacto corporativa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Socovesa</t>
+          <t>IVL Inversiones Inmobiliarias</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -1129,37 +1129,37 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS1 / DS15</t>
+          <t>DS19</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>socovesa.cl</t>
+          <t>ivl.cl</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>contacto@socovesa.cl</t>
+          <t>contacto@ivl.cl</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>+56 2 2520 4100</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Eliodoro Yáñez 2962 Providencia</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No — Valparaíso/Concepción/Frutillar</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1169,19 +1169,19 @@
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Página de subsidios del sitio</t>
+          <t>Página de contacto</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Urbani</t>
+          <t>Pilares (Grupo Socovesa)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>Inmobiliaria / portal</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1191,32 +1191,32 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>urbani.cl</t>
+          <t>pilares.cl</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>contacto@urbani.cl</t>
+          <t>servicioalcliente@pilares.cl</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>+56 41 246 2278</t>
+          <t>+56 2 2840 7832</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Barros Arana 1098 of. 1705 Concepción</t>
+          <t>Providencia</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Parcial — opera nacional desde Concepción</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -1226,14 +1226,14 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Página de contacto</t>
+          <t>Página de postventa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Inmobiliaria Noval</t>
+          <t>Siena Inmobiliaria</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1243,27 +1243,27 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS1 / DS49 colectivo</t>
+          <t>DS19 / DS1</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>inoval.cl</t>
+          <t>siena.cl</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>postventainoval@inoval.cl (postventa)</t>
+          <t>informes@sienainmobiliaria.com</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>+56 2 2902 0600</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Los Militares 6191 piso 12 Las Condes</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -1276,21 +1276,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>media</t>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>Página de contacto</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Maestra Inmobiliaria</t>
+          <t>Socovesa</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1300,131 +1300,131 @@
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>DS19</t>
+          <t>DS19 / DS1 / DS15</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>maestra.cl</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>No publicado (solo denuncias@maestra.cl)</t>
+          <t>socovesa.cl</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>contacto@socovesa.cl</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2940 9700</t>
+          <t>+56 2 2520 4100</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>Av. Las Condes 14157 Las Condes</t>
+          <t>Eliodoro Yáñez 2962 Providencia</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Sí — Presidente Prieto (P. Aguirre Cerda) y Brisas de Quilicura</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="12" t="inlineStr">
-        <is>
-          <t>baja</t>
+          <t>ADI</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Página DS19 del sitio</t>
+          <t>Página de subsidios del sitio</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Albores</t>
+          <t>Urbani</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Inmobiliaria / portal</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS19 / DS1</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>urbani.cl</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>contacto@urbani.cl</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 41 246 2278</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Barros Arana 1098 of. 1705 Concepción</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Parcial — opera nacional desde Concepción</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Página de contacto</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Ciclos</t>
+          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Fundación / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS49 / DS19</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>urbanismosocial.cl</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>francisco@urbanismosocial.cl</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I18" s="8" t="inlineStr">
@@ -1447,21 +1447,21 @@
           <t>ADVS</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Consolida</t>
+          <t>Inmobiliaria Noval</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1471,89 +1471,89 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS19 / DS1 / DS49 colectivo</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inoval.cl</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>postventainoval@inoval.cl (postventa)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2902 0600</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>media</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Sitio corporativo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Constructora OVAL (entidad patrocinante)</t>
+          <t>Maestra Inmobiliaria</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Constructora / Entidad Patrocinante</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>DS49 / DS19</t>
+          <t>DS19</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>constructoraoval.cl</t>
+          <t>maestra.cl</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado (solo denuncias@maestra.cl)</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2343 0660</t>
+          <t>+56 2 2940 9700</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>Av. Pdte. Kennedy 5682 Vitacura</t>
+          <t>Av. Las Condes 14157 Las Condes</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí — Presidente Prieto (P. Aguirre Cerda) y Brisas de Quilicura</t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
@@ -1561,21 +1561,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>baja</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>Página de entidad patrocinante del sitio</t>
+          <t>Página DS19 del sitio</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Convet</t>
+          <t>Albores</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1585,17 +1585,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DS19</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>convet.cl</t>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1605,17 +1605,17 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Sí — proyecto en Independencia</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
@@ -1625,14 +1625,14 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Ecomac</t>
+          <t>Ciclos</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -1642,37 +1642,37 @@
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>DS19 / Plan de Emergencia Habitacional</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>ecomac.cl</t>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2964 3999</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>Rosario Norte 532 piso 9 Las Condes (oficina Santiago)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Sí — oficina Santiago</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Página de sucursales</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Grupo Vías</t>
+          <t>Convet</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1699,17 +1699,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
+          <t>DS19</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>convet.cl</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>No publicado (formulario web)</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1719,17 +1719,17 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí — proyecto en Independencia</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
@@ -1739,14 +1739,14 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Sitio corporativo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Identidades</t>
+          <t>Ecomac</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1756,37 +1756,37 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>DS19</t>
-        </is>
-      </c>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>No identificado</t>
+          <t>DS19 / Plan de Emergencia Habitacional</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>ecomac.cl</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>No publicado (formulario web)</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2964 3999</t>
         </is>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Rosario Norte 532 piso 9 Las Condes (oficina Santiago)</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí — oficina Santiago</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1796,14 +1796,14 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Página de sucursales</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Inmobiliaria CISS</t>
+          <t>Grupo Vías</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
@@ -1813,17 +1813,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>DS19</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>ciss.cl</t>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>No — Gran Concepción</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -1853,14 +1853,14 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Inmobiliaria Los Silos</t>
+          <t>Inmobiliaria CISS</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1875,27 +1875,27 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>ilossilos.cl</t>
+          <t>ciss.cl</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>No publicado (correo por proyecto)</t>
+          <t>No publicado (formulario web)</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2811 4261</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
-          <t>El Manzano 867 Padre Hurtado</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="H26" s="9" t="inlineStr">
         <is>
-          <t>Sí — Padre Hurtado y Renca</t>
+          <t>No — Gran Concepción</t>
         </is>
       </c>
       <c r="I26" s="8" t="inlineStr">
@@ -1910,14 +1910,14 @@
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>Página de subsidios del sitio</t>
+          <t>Sitio corporativo</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Nexos Desarrollos Inmobiliarios</t>
+          <t>Inmobiliaria Los Silos</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -1930,34 +1930,34 @@
           <t>DS19</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>ilossilos.cl</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>No publicado (correo por proyecto)</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2811 4261</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>El Manzano 867 Padre Hurtado</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Sí — proyectos DS19 en RM UF 2.300-2.750</t>
+          <t>Sí — Padre Hurtado y Renca</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J27" s="13" t="inlineStr">
@@ -1967,14 +1967,14 @@
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Listado de proyectos DS19 RM</t>
+          <t>Página de subsidios del sitio</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>PY Inmobiliaria</t>
+          <t>Nexos Desarrollos Inmobiliarios</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1987,34 +1987,34 @@
           <t>DS19</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>py.cl</t>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>No publicado (ejecutivo por zona)</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2439 3500</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
-          <t>Suecia 0142 of. 901 Providencia</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H28" s="9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sí — proyectos DS19 en RM UF 2.300-2.750</t>
         </is>
       </c>
       <c r="I28" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J28" s="13" t="inlineStr">
@@ -2024,44 +2024,44 @@
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>Página DS19 del sitio</t>
+          <t>Listado de proyectos DS19 RM</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
+          <t>PY Inmobiliaria</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Fundación / Entidad Patrocinante</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>DS49 / DS19</t>
+          <t>DS19</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>urbanismosocial.cl</t>
+          <t>py.cl</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>No publicado (formulario web)</t>
+          <t>No publicado (ejecutivo por zona)</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2439 3500</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>Suecia 0142 of. 901 Providencia</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>Página DS19 del sitio</t>
         </is>
       </c>
     </row>
@@ -2210,33 +2210,37 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D21" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D22" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D25" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D11" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D13" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D14" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D20" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D24" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D26" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D31" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2248,7 +2252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2395,7 +2399,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Inmobiliaria Noval</t>
+          <t>Consolida</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -2405,27 +2409,27 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>DS19 / DS1 / DS49 colectivo</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>inoval.cl</t>
+          <t>DS19 / DS49</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
         <is>
-          <t>postventainoval@inoval.cl (postventa)</t>
+          <t>contacto@consolida.cl</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2902 0600</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>Santiago</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -2435,91 +2439,91 @@
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>media</t>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>Sitio corporativo</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Albores</t>
+          <t>Constructora OVAL (entidad patrocinante)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Constructora / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS49 / DS19</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>constructoraoval.cl</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ggajardo@constructoraoval.cl</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2343 0660</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Av. Pdte. Kennedy 5682 Vitacura</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Ciclos</t>
+          <t>Consultora e Inmobiliaria Hogar SpA</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
+          <t>DS49</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -2527,9 +2531,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>cristian.lecaros@gmail.com</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -2539,44 +2543,44 @@
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Región Metropolitana</t>
         </is>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Consolida</t>
+          <t>Consultora V y S Ltda</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
+          <t>DS49</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -2584,9 +2588,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>consultoraveyese@gmail.com</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2596,64 +2600,64 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Región Metropolitana</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Constructora OVAL (entidad patrocinante)</t>
+          <t>Emile Straub y Compañía Ltda</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Constructora / Entidad Patrocinante</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>DS49 / DS19</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>constructoraoval.cl</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>No publicado (formulario web)</t>
+          <t>DS49</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>No identificado</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>emilestraubbarros@gmail.com</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>+56 2 2343 0660</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
-          <t>Av. Pdte. Kennedy 5682 Vitacura</t>
+          <t>Región Metropolitana</t>
         </is>
       </c>
       <c r="H10" s="9" t="inlineStr">
@@ -2666,21 +2670,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>Página de entidad patrocinante del sitio</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Consultora e Inmobiliaria Hogar SpA</t>
+          <t>Entidad Organizadora y Consultora Habitacional Miraflores SpA</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -2698,9 +2702,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>ameyer@constructoracasahogar.cl</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2723,21 +2727,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Consultora V y S Ltda</t>
+          <t>Entidad Patrocinante Kutralwe Ltda</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -2755,9 +2759,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>lorena.pino@kutralwe.com</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -2767,7 +2771,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -2780,21 +2784,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>DOMUM Entidad Patrocinante SpA</t>
+          <t>Evolutiva Entidad Patrocinante y Consultora de Vivienda y Urbanismo SpA</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
@@ -2812,9 +2816,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>ep.evolutiva@gmail.com</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2824,7 +2828,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
@@ -2837,21 +2841,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Emile Straub y Compañía Ltda</t>
+          <t>Gestora Mashogar Ltda</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -2869,9 +2873,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>marcelofg@gestoramashogar.cl</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -2881,7 +2885,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -2894,26 +2898,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Entidad Organizadora y Consultora Habitacional Miraflores SpA</t>
+          <t>Ilustre Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Municipio / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2921,14 +2925,14 @@
           <t>DS49</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>huechuraba.cl</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>paulina.trivino@huechuraba.cl</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2938,7 +2942,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>Huechuraba</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -2951,26 +2955,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante Jessica Sandoval Quiroga E.I.R.L.</t>
+          <t>Inmobiliaria y Constructora INSOC Ltda</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Constructora / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -2983,9 +2987,9 @@
           <t>No identificado</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+      <c r="E16" s="10" t="inlineStr">
+        <is>
+          <t>j.elicer@insoc.cl</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -2995,7 +2999,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Región Metropolitana</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -3008,41 +3012,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante Kutralwe Ltda</t>
+          <t>TECHO-Chile (Inmobiliaria Social)</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Fundación / desarrolladora</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DS49</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS49 colectivo</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>cl.techo.org</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>capellania@techo.org</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -3052,7 +3056,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
@@ -3062,44 +3066,44 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante Manuel Medina E.I.R.L.</t>
+          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Fundación / Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>DS49</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS49 / DS19</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>urbanismosocial.cl</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>francisco@urbanismosocial.cl</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -3109,7 +3113,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -3119,54 +3123,54 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>alta</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>nomina MINVU junio 2026 (PDF oficial)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Evolutiva Entidad Patrocinante y Consultora de Vivienda y Urbanismo SpA</t>
+          <t>Inmobiliaria Noval</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>DS49</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
+          <t>DS19 / DS1 / DS49 colectivo</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>inoval.cl</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>postventainoval@inoval.cl (postventa)</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>+56 2 2902 0600</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Santiago</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
@@ -3179,31 +3183,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>media</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>Sitio corporativo</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Fundación Deportistas por un Sueño</t>
+          <t>Albores</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Fundación</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>DS49</t>
+          <t>DS19 / DS49</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -3250,17 +3254,17 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Gestora Mashogar Ltda</t>
+          <t>Ciclos</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>DS49</t>
+          <t>DS19 / DS49</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3285,12 +3289,12 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
@@ -3300,24 +3304,24 @@
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Grupo Vías</t>
+          <t>DOMUM Entidad Patrocinante SpA</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>Inmobiliaria</t>
+          <t>Entidad Patrocinante</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>DS19 / DS49</t>
+          <t>DS49</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -3337,17 +3341,17 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>No publicado</t>
+          <t>Región Metropolitana</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
         <is>
-          <t>Por confirmar</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I22" s="8" t="inlineStr">
         <is>
-          <t>ADVS</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -3357,19 +3361,19 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>Nómina de socios ADVS</t>
+          <t>Citada en documento MINVU antiguo; NO aparece en la nómina de junio 2026</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Huechuraba</t>
+          <t>Fundación Deportistas por un Sueño</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Municipio / Entidad Patrocinante</t>
+          <t>Fundación</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3377,9 +3381,9 @@
           <t>DS49</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>huechuraba.cl</t>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>No identificado</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -3394,17 +3398,17 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Huechuraba</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
@@ -3414,24 +3418,24 @@
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Inmobiliaria D&amp;M SpA</t>
+          <t>Grupo Vías</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>Entidad Patrocinante / Inmobiliaria</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>DS49</t>
+          <t>DS19 / DS49</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -3456,12 +3460,12 @@
       </c>
       <c r="H24" s="9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I24" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -3471,24 +3475,24 @@
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
+          <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Inmobiliaria y Constructora INSOC Ltda</t>
+          <t>Urbanitas</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Constructora / Entidad Patrocinante</t>
+          <t>Inmobiliaria</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>DS49</t>
+          <t>DS19 / DS49</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -3508,17 +3512,17 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Región Metropolitana</t>
+          <t>No publicado</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Por confirmar</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>ADVS</t>
         </is>
       </c>
       <c r="J25" s="13" t="inlineStr">
@@ -3528,297 +3532,12 @@
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>Nómina MINVU de entidades patrocinantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Nahuen Ingenieros Constructores Asociados SpA</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Patrocinante / Constructora</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>DS49</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="H26" s="9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
-        </is>
-      </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>TECHO-Chile (Inmobiliaria Social)</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Fundación / desarrolladora</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>DS49 colectivo</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>cl.techo.org</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>No publicado (formulario web)</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>Página Inmobiliaria Social</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>Urbanismo Social / Fundación Gestión Vivienda</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>Fundación / Entidad Patrocinante</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>DS49 / DS19</t>
-        </is>
-      </c>
-      <c r="D28" s="10" t="inlineStr">
-        <is>
-          <t>urbanismosocial.cl</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>No publicado (formulario web)</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
-        <is>
-          <t>Santiago</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I28" s="8" t="inlineStr">
-        <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
-        </is>
-      </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>Sitio corporativo</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>Urbanitas</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Inmobiliaria</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>DS19 / DS49</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Por confirmar</t>
-        </is>
-      </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>ADVS</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
-        <is>
           <t>Nómina de socios ADVS</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Ávalos y Ibacache Arquitectos Sociales Ltda</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>Entidad Patrocinante</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>DS49</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>No identificado</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>No publicado</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="I30" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>sin dato</t>
-        </is>
-      </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>Nómina MINVU junio 2026 (vía índice de búsqueda)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:K30"/>
+  <autoFilter ref="A4:K25"/>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
@@ -3826,12 +3545,25 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D10" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D23" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D27" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D28" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D18" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3883,7 +3615,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -3893,7 +3625,7 @@
         </is>
       </c>
       <c r="B6" s="15" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7">
@@ -3903,7 +3635,7 @@
         </is>
       </c>
       <c r="B7" s="15" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
